--- a/databases/STEAM_DB.xlsx
+++ b/databases/STEAM_DB.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SteamBOQ_AI\databases\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects_AI\SteamBOQ_AI\databases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F2335E1-F209-4CC9-A132-C31F7E74CAD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6CC2F13-0B7F-44A1-AE76-7EE4252FAEF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D4F90B61-8EB2-4F3B-A7BB-1ACEB4FA5283}"/>
+    <workbookView xWindow="1812" yWindow="1812" windowWidth="17280" windowHeight="8964" xr2:uid="{D4F90B61-8EB2-4F3B-A7BB-1ACEB4FA5283}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="Steam_Properties" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,25 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
-  <si>
-    <t>Pressure (barg)</t>
-  </si>
-  <si>
-    <t>Sat Temp (°C)</t>
-  </si>
-  <si>
-    <t>hf (kJ/kg)</t>
-  </si>
-  <si>
-    <t>hfg (kJ/kg)</t>
-  </si>
-  <si>
-    <t>hg (kJ/kg)</t>
-  </si>
-  <si>
-    <t>Specific Volume Steam (m3/kg)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>hf = Enthalpy of Saturated Liquid</t>
   </si>
@@ -61,6 +43,33 @@
   </si>
   <si>
     <t>Specific Volume of Steam</t>
+  </si>
+  <si>
+    <t>Pressure_barg</t>
+  </si>
+  <si>
+    <t>hf_kJkg</t>
+  </si>
+  <si>
+    <t>hfg_kJkg</t>
+  </si>
+  <si>
+    <t>hg_kJkg</t>
+  </si>
+  <si>
+    <t>Sat_Temp_C</t>
+  </si>
+  <si>
+    <t>Specific_Volume_Steam_m3kg</t>
+  </si>
+  <si>
+    <t>Dynamic_Viscosity_kg_ms</t>
+  </si>
+  <si>
+    <t>Density_water_kgm3</t>
+  </si>
+  <si>
+    <t>Dynamic_Viscosity_water_kg_ms</t>
   </si>
 </sst>
 </file>
@@ -95,7 +104,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -118,14 +127,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -440,7 +470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49348902-0F99-445E-83B7-70EED4BFC1E9}">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.77734375" bestFit="1" customWidth="1"/>
@@ -449,29 +479,40 @@
     <col min="4" max="4" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -490,8 +531,18 @@
       <c r="F2" s="1">
         <v>1.694</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G2" s="5">
+        <v>1.17E-5</v>
+      </c>
+      <c r="H2" s="6">
+        <v>958.4</v>
+      </c>
+      <c r="I2" s="6">
+        <v>2.8200000000000002E-4</v>
+      </c>
+      <c r="J2" s="4"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -510,8 +561,18 @@
       <c r="F3" s="1">
         <v>0.88500000000000001</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G3" s="5">
+        <v>1.26E-5</v>
+      </c>
+      <c r="H3" s="6">
+        <v>946.1</v>
+      </c>
+      <c r="I3" s="6">
+        <v>2.4000000000000001E-4</v>
+      </c>
+      <c r="J3" s="4"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -530,8 +591,18 @@
       <c r="F4" s="1">
         <v>0.60499999999999998</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G4" s="5">
+        <v>1.33E-5</v>
+      </c>
+      <c r="H4" s="6">
+        <v>938</v>
+      </c>
+      <c r="I4" s="6">
+        <v>2.2000000000000001E-4</v>
+      </c>
+      <c r="J4" s="4"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -550,8 +621,18 @@
       <c r="F5" s="1">
         <v>0.46200000000000002</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G5" s="5">
+        <v>1.3900000000000001E-5</v>
+      </c>
+      <c r="H5" s="6">
+        <v>930.5</v>
+      </c>
+      <c r="I5" s="6">
+        <v>2.04E-4</v>
+      </c>
+      <c r="J5" s="4"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -570,8 +651,18 @@
       <c r="F6" s="1">
         <v>0.375</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G6" s="5">
+        <v>1.4399999999999999E-5</v>
+      </c>
+      <c r="H6" s="6">
+        <v>923.8</v>
+      </c>
+      <c r="I6" s="6">
+        <v>1.92E-4</v>
+      </c>
+      <c r="J6" s="4"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -590,8 +681,18 @@
       <c r="F7" s="1">
         <v>0.315</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G7" s="5">
+        <v>1.4800000000000001E-5</v>
+      </c>
+      <c r="H7" s="6">
+        <v>917</v>
+      </c>
+      <c r="I7" s="6">
+        <v>1.8200000000000001E-4</v>
+      </c>
+      <c r="J7" s="4"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -610,8 +711,18 @@
       <c r="F8" s="1">
         <v>0.27100000000000002</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G8" s="5">
+        <v>1.52E-5</v>
+      </c>
+      <c r="H8" s="6">
+        <v>911</v>
+      </c>
+      <c r="I8" s="6">
+        <v>1.73E-4</v>
+      </c>
+      <c r="J8" s="4"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -630,8 +741,18 @@
       <c r="F9" s="1">
         <v>0.23799999999999999</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G9" s="5">
+        <v>1.56E-5</v>
+      </c>
+      <c r="H9" s="6">
+        <v>904.8</v>
+      </c>
+      <c r="I9" s="6">
+        <v>1.66E-4</v>
+      </c>
+      <c r="J9" s="4"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -650,8 +771,18 @@
       <c r="F10" s="1">
         <v>0.21199999999999999</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G10" s="5">
+        <v>1.5999999999999999E-5</v>
+      </c>
+      <c r="H10" s="6">
+        <v>899</v>
+      </c>
+      <c r="I10" s="6">
+        <v>1.5899999999999999E-4</v>
+      </c>
+      <c r="J10" s="4"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -670,8 +801,18 @@
       <c r="F11" s="1">
         <v>0.191</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G11" s="5">
+        <v>1.63E-5</v>
+      </c>
+      <c r="H11" s="6">
+        <v>893.3</v>
+      </c>
+      <c r="I11" s="6">
+        <v>1.5300000000000001E-4</v>
+      </c>
+      <c r="J11" s="4"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -690,8 +831,18 @@
       <c r="F12" s="1">
         <v>0.17399999999999999</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G12" s="5">
+        <v>1.66E-5</v>
+      </c>
+      <c r="H12" s="6">
+        <v>887</v>
+      </c>
+      <c r="I12" s="6">
+        <v>1.4799999999999999E-4</v>
+      </c>
+      <c r="J12" s="4"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -710,8 +861,18 @@
       <c r="F13" s="1">
         <v>0.14799999999999999</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G13" s="5">
+        <v>1.7200000000000001E-5</v>
+      </c>
+      <c r="H13" s="6">
+        <v>876.5</v>
+      </c>
+      <c r="I13" s="6">
+        <v>1.3999999999999999E-4</v>
+      </c>
+      <c r="J13" s="4"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>15</v>
       </c>
@@ -730,8 +891,17 @@
       <c r="F14" s="1">
         <v>0.13200000000000001</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G14" s="5">
+        <v>1.8099999999999999E-5</v>
+      </c>
+      <c r="H14" s="6">
+        <v>861.5</v>
+      </c>
+      <c r="I14" s="6">
+        <v>1.2899999999999999E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>20</v>
       </c>
@@ -750,86 +920,137 @@
       <c r="F15" s="1">
         <v>9.9000000000000005E-2</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G15" s="5">
+        <v>1.9300000000000002E-5</v>
+      </c>
+      <c r="H15" s="6">
+        <v>842</v>
+      </c>
+      <c r="I15" s="6">
+        <v>1.16E-4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>25</v>
       </c>
       <c r="B16" s="1">
         <v>223.99</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="H16" s="6">
+        <v>825</v>
+      </c>
+      <c r="I16" s="6">
+        <v>1.07E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>30</v>
       </c>
       <c r="B17" s="1">
         <v>233.9</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="H17" s="6">
+        <v>808</v>
+      </c>
+      <c r="I17" s="6">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>40</v>
       </c>
       <c r="B18" s="1">
         <v>250.4</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="H18" s="6">
+        <v>777</v>
+      </c>
+      <c r="I18" s="6">
+        <v>8.7999999999999998E-5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>50</v>
       </c>
       <c r="B19" s="1">
         <v>263.99</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="H19" s="6">
+        <v>748</v>
+      </c>
+      <c r="I19" s="6">
+        <v>7.8999999999999996E-5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>60</v>
       </c>
       <c r="B20" s="1">
         <v>275.64</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="H20" s="6">
+        <v>722</v>
+      </c>
+      <c r="I20" s="6">
+        <v>7.2000000000000002E-5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>80</v>
       </c>
       <c r="B21" s="1">
         <v>295.06</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="H21" s="6">
+        <v>676</v>
+      </c>
+      <c r="I21" s="6">
+        <v>6.2000000000000003E-5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>100</v>
       </c>
       <c r="B22" s="1">
         <v>311.06</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="H22" s="6">
+        <v>633</v>
+      </c>
+      <c r="I22" s="6">
+        <v>5.5000000000000002E-5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
